--- a/数据匹配结果.xlsx
+++ b/数据匹配结果.xlsx
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.407</v>
+        <v>0.3272</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.6169</v>
+        <v>0.5606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4317</v>
+        <v>0.4301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.2696</v>
+        <v>0.2514</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1374,11 +1374,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">皮带智能巡检机器人项目 </t>
+          <t xml:space="preserve">电解阴极板自动打磨校正项目 </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.2328</v>
+        <v>0.125</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.2805</v>
+        <v>0.3696</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.1111</v>
+        <v>0.1</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.4402</v>
+        <v>0.4798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.7571</v>
+        <v>0.8205</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7913</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.7216</v>
+        <v>0.7944</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.7347</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.7347</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.6748</v>
+        <v>0.7264</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8763</v>
+        <v>0.8098</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8619</v>
+        <v>0.8393</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.8126</v>
+        <v>0.77</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.7669</v>
+        <v>0.729</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8141</v>
+        <v>0.8421</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5735</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5735</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5735</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.5686</v>
+        <v>0.5622</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2214,11 +2214,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>焙烧制酸和湿法工艺控制系统改扩建项目</t>
+          <t>原料智能盘库系统建设项目</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.2219</v>
+        <v>0.1973</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.2508</v>
+        <v>0.2945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.7091</v>
+        <v>0.7006</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.6927</v>
+        <v>0.7687</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.6224</v>
+        <v>0.7039</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.5246</v>
+        <v>0.5988</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.5099</v>
+        <v>0.5845</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.3</v>
+        <v>0.331</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.1553</v>
+        <v>0.1856</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0625</v>
+        <v>0.0769</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.1892</v>
+        <v>0.2234</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2970,11 +2970,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>16万吨扩产DCS系统优化工作</t>
+          <t>圆盘给料机上料系统技改项目</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.175</v>
+        <v>0.2167</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.2203</v>
+        <v>0.125</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.2319</v>
+        <v>0.1457</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.2428</v>
+        <v>0.1739</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3082,11 +3082,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>圆盘给料机上料系统技改项目</t>
+          <t>废液循环池自动抽阳极泥系统技改项目</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.1962</v>
+        <v>0.1136</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3110,11 +3110,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>窑渣自动取样、实时化验分析系统技改项目</t>
+          <t>废液循环池自动抽阳极泥系统技改项目</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.1873</v>
+        <v>0.1978</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.1353</v>
+        <v>0.1584</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.3477</v>
+        <v>0.3701</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.2471</v>
+        <v>0.2679</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.256</v>
+        <v>0.2787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.2902</v>
+        <v>0.3248</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.125</v>
+        <v>0.1538</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.1663</v>
+        <v>0.1833</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.2866</v>
+        <v>0.3092</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.2218</v>
+        <v>0.2433</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.1722</v>
+        <v>0.1879</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.1614</v>
+        <v>0.19</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1154</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.1866</v>
+        <v>0.2241</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.1333</v>
+        <v>0.119</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.9392</v>
+        <v>1</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0.9064</v>
+        <v>1</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0.8653</v>
+        <v>1</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>0.7585</v>
+        <v>0.7619</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -5714,11 +5714,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>露采无人驾驶矿卡项目</t>
+          <t>统一数据平台</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0.1538</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0.8282</v>
+        <v>1</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0.6489</v>
+        <v>0.5829</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>0.6803</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>0.9046</v>
+        <v>0.887</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>0.9636</v>
+        <v>0.962</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>0.4449</v>
+        <v>0.4862</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -6110,11 +6110,11 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>0.5266</v>
+        <v>0.462</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>匹配成功</t>
+          <t>匹配不成功</t>
         </is>
       </c>
     </row>
@@ -6138,11 +6138,11 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>0.5281</v>
+        <v>0.4555</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>匹配成功</t>
+          <t>匹配不成功</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>0.6291</v>
+        <v>0.6105</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>0.6071</v>
+        <v>0.5878</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>0.5998</v>
+        <v>0.5805</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>0.5968</v>
+        <v>0.5775</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>0.5968</v>
+        <v>0.5775</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>0.349</v>
+        <v>0.3761</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -6362,11 +6362,11 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>0.5092</v>
+        <v>0.486</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>匹配成功</t>
+          <t>匹配不成功</t>
         </is>
       </c>
     </row>
@@ -6390,11 +6390,11 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.4835</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>匹配成功</t>
+          <t>匹配不成功</t>
         </is>
       </c>
     </row>
@@ -6414,11 +6414,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>紫金铜业智能取制样项目</t>
+          <t>紫金铜业智能工厂无线网络系统项目</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>0.2688</v>
+        <v>0.2731</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -6442,11 +6442,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>紫金铜业智能取制样项目</t>
+          <t>紫金铜业阳极板自动钻样系统</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>0.2379</v>
+        <v>0.1946</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>0.7963</v>
+        <v>0.7611</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>0.2504</v>
+        <v>0.2188</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8183</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>0.4135</v>
+        <v>0.3643</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>0.6843</v>
+        <v>0.8066</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -7254,11 +7254,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>二期扩建自动化系统</t>
+          <t>安全生产管控平台</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>0.125</v>
+        <v>0.1538</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>0.1176</v>
+        <v>0.1071</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>0.0769</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>0.8619</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>0.2432</v>
+        <v>0.2586</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>0.643</v>
+        <v>0.601</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>0.6506</v>
+        <v>0.6105</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>0.7312</v>
+        <v>0.7077</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>0.643</v>
+        <v>0.601</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.6651</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>0.8139</v>
+        <v>1</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4">
@@ -16043,7 +16043,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>36.13%</t>
+          <t>35.46%</t>
         </is>
       </c>
     </row>
@@ -17153,10 +17153,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C45" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>65.38%</t>
+          <t>50.00%</t>
         </is>
       </c>
     </row>
